--- a/output/casestudy_20260909.xlsx
+++ b/output/casestudy_20260909.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>10.75923490000014</v>
+        <v>9.720187899999473</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>10.71078539999962</v>
+        <v>9.336839499999769</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7.098356999999851</v>
+        <v>6.239021699999284</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>11.1891585999997</v>
+        <v>9.812759500000539</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>11.61983889999965</v>
+        <v>11.4412983000002</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>8.940638700000363</v>
+        <v>8.475321400001121</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>11.17275980000022</v>
+        <v>10.67408410000098</v>
       </c>
     </row>
     <row r="9">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>11.26285049999979</v>
+        <v>12.49239999999918</v>
       </c>
     </row>
     <row r="10">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>15.34185310000021</v>
+        <v>14.78918150000027</v>
       </c>
     </row>
     <row r="11">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>8.548272900000029</v>
+        <v>9.034406100001434</v>
       </c>
     </row>
     <row r="12">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>6.952895700000226</v>
+        <v>7.626277899998968</v>
       </c>
     </row>
   </sheetData>
@@ -13998,7 +13998,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10.8 초</t>
+          <t>9.7 초</t>
         </is>
       </c>
     </row>
@@ -14010,7 +14010,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10.7 초</t>
+          <t>9.3 초</t>
         </is>
       </c>
     </row>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7.1 초</t>
+          <t>6.2 초</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11.2 초</t>
+          <t>9.8 초</t>
         </is>
       </c>
     </row>
@@ -14046,7 +14046,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11.6 초</t>
+          <t>11.4 초</t>
         </is>
       </c>
     </row>
@@ -14058,7 +14058,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8.9 초</t>
+          <t>8.5 초</t>
         </is>
       </c>
     </row>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11.2 초</t>
+          <t>10.7 초</t>
         </is>
       </c>
     </row>
@@ -14082,7 +14082,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11.3 초</t>
+          <t>12.5 초</t>
         </is>
       </c>
     </row>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15.3 초</t>
+          <t>14.8 초</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>8.5 초</t>
+          <t>9.0 초</t>
         </is>
       </c>
     </row>
@@ -14118,7 +14118,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7.0 초</t>
+          <t>7.6 초</t>
         </is>
       </c>
     </row>
@@ -14130,7 +14130,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>121.5 초</t>
+          <t>117.5 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260909.xlsx
+++ b/output/casestudy_20260909.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>9.720187899999473</v>
+        <v>9.641476799999509</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>9.336839499999769</v>
+        <v>9.573348100000658</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>6.239021699999284</v>
+        <v>6.304151000000275</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>9.812759500000539</v>
+        <v>9.928847099999984</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>11.4412983000002</v>
+        <v>10.56991129999915</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>8.475321400001121</v>
+        <v>8.228498799999215</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>10.67408410000098</v>
+        <v>10.22858219999944</v>
       </c>
     </row>
     <row r="9">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>12.49239999999918</v>
+        <v>10.3420444000003</v>
       </c>
     </row>
     <row r="10">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>14.78918150000027</v>
+        <v>14.05518589999883</v>
       </c>
     </row>
     <row r="11">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>9.034406100001434</v>
+        <v>7.285893299998861</v>
       </c>
     </row>
     <row r="12">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>7.626277899998968</v>
+        <v>6.398549699999421</v>
       </c>
     </row>
   </sheetData>
@@ -13998,7 +13998,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9.7 초</t>
+          <t>9.6 초</t>
         </is>
       </c>
     </row>
@@ -14010,7 +14010,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>9.3 초</t>
+          <t>9.6 초</t>
         </is>
       </c>
     </row>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6.2 초</t>
+          <t>6.3 초</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9.8 초</t>
+          <t>9.9 초</t>
         </is>
       </c>
     </row>
@@ -14046,7 +14046,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11.4 초</t>
+          <t>10.6 초</t>
         </is>
       </c>
     </row>
@@ -14058,7 +14058,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8.5 초</t>
+          <t>8.2 초</t>
         </is>
       </c>
     </row>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10.7 초</t>
+          <t>10.2 초</t>
         </is>
       </c>
     </row>
@@ -14082,7 +14082,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12.5 초</t>
+          <t>10.3 초</t>
         </is>
       </c>
     </row>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14.8 초</t>
+          <t>14.1 초</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>9.0 초</t>
+          <t>7.3 초</t>
         </is>
       </c>
     </row>
@@ -14118,7 +14118,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7.6 초</t>
+          <t>6.4 초</t>
         </is>
       </c>
     </row>
@@ -14130,7 +14130,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>117.5 초</t>
+          <t>109.7 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260909.xlsx
+++ b/output/casestudy_20260909.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>9.641476799999509</v>
+        <v>9.703410800000711</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>9.573348100000658</v>
+        <v>9.679135999998834</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>6.304151000000275</v>
+        <v>6.352371400000266</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>9.928847099999984</v>
+        <v>9.863432499998453</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>10.56991129999915</v>
+        <v>10.4902820999996</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>8.228498799999215</v>
+        <v>8.212671299999784</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>10.22858219999944</v>
+        <v>10.18891010000152</v>
       </c>
     </row>
     <row r="9">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>10.3420444000003</v>
+        <v>10.23405079999793</v>
       </c>
     </row>
     <row r="10">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>14.05518589999883</v>
+        <v>13.99265930000183</v>
       </c>
     </row>
     <row r="11">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>7.285893299998861</v>
+        <v>7.320899599999393</v>
       </c>
     </row>
     <row r="12">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>6.398549699999421</v>
+        <v>6.218959599998925</v>
       </c>
     </row>
   </sheetData>
@@ -13998,7 +13998,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9.6 초</t>
+          <t>9.7 초</t>
         </is>
       </c>
     </row>
@@ -14010,7 +14010,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>9.6 초</t>
+          <t>9.7 초</t>
         </is>
       </c>
     </row>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6.3 초</t>
+          <t>6.4 초</t>
         </is>
       </c>
     </row>
@@ -14046,7 +14046,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10.6 초</t>
+          <t>10.5 초</t>
         </is>
       </c>
     </row>
@@ -14082,7 +14082,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10.3 초</t>
+          <t>10.2 초</t>
         </is>
       </c>
     </row>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14.1 초</t>
+          <t>14.0 초</t>
         </is>
       </c>
     </row>
@@ -14118,7 +14118,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6.4 초</t>
+          <t>6.2 초</t>
         </is>
       </c>
     </row>
@@ -14130,7 +14130,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>109.7 초</t>
+          <t>109.5 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260909.xlsx
+++ b/output/casestudy_20260909.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>9.703410800000711</v>
+        <v>10.04200449999917</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>9.679135999998834</v>
+        <v>10.14983420000135</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>6.352371400000266</v>
+        <v>6.501720099997328</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>9.863432499998453</v>
+        <v>10.20807710000008</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>10.4902820999996</v>
+        <v>11.14283799999976</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>8.212671299999784</v>
+        <v>8.477508999996644</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>10.18891010000152</v>
+        <v>10.31502209999962</v>
       </c>
     </row>
     <row r="9">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>10.23405079999793</v>
+        <v>10.81242029999703</v>
       </c>
     </row>
     <row r="10">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>13.99265930000183</v>
+        <v>14.79014200000165</v>
       </c>
     </row>
     <row r="11">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>7.320899599999393</v>
+        <v>7.707566000000952</v>
       </c>
     </row>
     <row r="12">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>6.218959599998925</v>
+        <v>6.663741399999708</v>
       </c>
     </row>
   </sheetData>
@@ -13998,7 +13998,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9.7 초</t>
+          <t>10.0 초</t>
         </is>
       </c>
     </row>
@@ -14010,7 +14010,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>9.7 초</t>
+          <t>10.1 초</t>
         </is>
       </c>
     </row>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6.4 초</t>
+          <t>6.5 초</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9.9 초</t>
+          <t>10.2 초</t>
         </is>
       </c>
     </row>
@@ -14046,7 +14046,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10.5 초</t>
+          <t>11.1 초</t>
         </is>
       </c>
     </row>
@@ -14058,7 +14058,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8.2 초</t>
+          <t>8.5 초</t>
         </is>
       </c>
     </row>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10.2 초</t>
+          <t>10.3 초</t>
         </is>
       </c>
     </row>
@@ -14082,7 +14082,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10.2 초</t>
+          <t>10.8 초</t>
         </is>
       </c>
     </row>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14.0 초</t>
+          <t>14.8 초</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7.3 초</t>
+          <t>7.7 초</t>
         </is>
       </c>
     </row>
@@ -14118,7 +14118,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6.2 초</t>
+          <t>6.7 초</t>
         </is>
       </c>
     </row>
@@ -14130,7 +14130,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>109.5 초</t>
+          <t>114.5 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260909.xlsx
+++ b/output/casestudy_20260909.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>10.04200449999917</v>
+        <v>12.09929990000091</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>10.14983420000135</v>
+        <v>11.47097419999773</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>6.501720099997328</v>
+        <v>8.091625200002454</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>10.20807710000008</v>
+        <v>14.72481659999903</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>11.14283799999976</v>
+        <v>14.21025409999856</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>8.477508999996644</v>
+        <v>12.25302229999943</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>10.31502209999962</v>
+        <v>13.2920054999995</v>
       </c>
     </row>
     <row r="9">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>10.81242029999703</v>
+        <v>11.36980230000336</v>
       </c>
     </row>
     <row r="10">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>14.79014200000165</v>
+        <v>15.0257380999974</v>
       </c>
     </row>
     <row r="11">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>7.707566000000952</v>
+        <v>7.816042499995092</v>
       </c>
     </row>
     <row r="12">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>6.663741399999708</v>
+        <v>6.686946800000442</v>
       </c>
     </row>
   </sheetData>
@@ -13998,7 +13998,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10.0 초</t>
+          <t>12.1 초</t>
         </is>
       </c>
     </row>
@@ -14010,7 +14010,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10.1 초</t>
+          <t>11.5 초</t>
         </is>
       </c>
     </row>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6.5 초</t>
+          <t>8.1 초</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10.2 초</t>
+          <t>14.7 초</t>
         </is>
       </c>
     </row>
@@ -14046,7 +14046,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11.1 초</t>
+          <t>14.2 초</t>
         </is>
       </c>
     </row>
@@ -14058,7 +14058,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8.5 초</t>
+          <t>12.3 초</t>
         </is>
       </c>
     </row>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10.3 초</t>
+          <t>13.3 초</t>
         </is>
       </c>
     </row>
@@ -14082,7 +14082,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10.8 초</t>
+          <t>11.4 초</t>
         </is>
       </c>
     </row>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14.8 초</t>
+          <t>15.0 초</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7.7 초</t>
+          <t>7.8 초</t>
         </is>
       </c>
     </row>
@@ -14130,7 +14130,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>114.5 초</t>
+          <t>135.3 초</t>
         </is>
       </c>
     </row>
